--- a/文档/政策.xlsx
+++ b/文档/政策.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Admin\Documents\GitHub\Sistine_civ6mod\文档\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
@@ -1018,7 +1023,7 @@
     <t>有2城区的城市+1宜居度</t>
   </si>
   <si>
-    <t>拥有至少2次升级的总督提供+2宜居度+1住房</t>
+    <t>总督提供+2宜居度+2住房</t>
   </si>
   <si>
     <t>总督加成</t>
@@ -4983,7 +4988,7 @@
       <c r="L47" s="6"/>
       <c r="U47" s="4"/>
     </row>
-    <row r="48" ht="40.5" spans="1:21">
+    <row r="48" ht="27" spans="1:21">
       <c r="E48" s="2" t="s">
         <v>150</v>
       </c>
